--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J259"/>
+  <dimension ref="A1:K259"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,6 +431,9 @@
       <c r="J1" t="str">
         <v>Tescil Önceliği</v>
       </c>
+      <c r="K1" t="str">
+        <v>İşlem Tarihi</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -871,7 +874,7 @@
         <v>Park</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>Dosya Hazırlandı</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -879,6 +882,9 @@
       <c r="J15" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K15" t="str">
+        <v>2026-04-07</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1319,7 +1325,7 @@
         <v>Park</v>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>Dosya Hazırlandı</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1327,6 +1333,9 @@
       <c r="J29" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K29" t="str">
+        <v>2026-04-07</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1351,7 +1360,7 @@
         <v>Park</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>Dosya Hazırlandı</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1359,6 +1368,9 @@
       <c r="J30" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K30" t="str">
+        <v>2026-04-07</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -8690,7 +8702,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J259"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K259"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -842,7 +842,7 @@
         <v>Otopark</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Dosya Hazırlandı</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -850,6 +850,9 @@
       <c r="J14" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K14" t="str">
+        <v>2026-04-07</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1459,13 +1462,16 @@
         <v>Park</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>Dosya Hazırlandı</v>
       </c>
       <c r="I33" t="str">
         <v/>
       </c>
       <c r="J33" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K33" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="34">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1497,13 +1497,16 @@
         <v>Park</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>Dosya Hazırlandı</v>
       </c>
       <c r="I34" t="str">
         <v/>
       </c>
       <c r="J34" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K34" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="35">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1168,13 +1168,16 @@
         <v>Park</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>Dosya Hazırlandı</v>
       </c>
       <c r="I24" t="str">
         <v/>
       </c>
       <c r="J24" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K24" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="25">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1168,7 +1168,7 @@
         <v>Park</v>
       </c>
       <c r="H24" t="str">
-        <v>Dosya Hazırlandı</v>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I24" t="str">
         <v/>

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -842,7 +842,7 @@
         <v>Otopark</v>
       </c>
       <c r="H14" t="str">
-        <v>Dosya Hazırlandı</v>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -877,7 +877,7 @@
         <v>Park</v>
       </c>
       <c r="H15" t="str">
-        <v>Dosya Hazırlandı</v>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -1331,7 +1331,7 @@
         <v>Park</v>
       </c>
       <c r="H29" t="str">
-        <v>Dosya Hazırlandı</v>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1366,7 +1366,7 @@
         <v>Park</v>
       </c>
       <c r="H30" t="str">
-        <v>Dosya Hazırlandı</v>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Park</v>
       </c>
       <c r="H33" t="str">
-        <v>Dosya Hazırlandı</v>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1500,7 +1500,7 @@
         <v>Park</v>
       </c>
       <c r="H34" t="str">
-        <v>Dosya Hazırlandı</v>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I34" t="str">
         <v/>

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1299,13 +1299,16 @@
         <v>Park</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I28" t="str">
         <v/>
       </c>
       <c r="J28" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K28" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="29">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -746,13 +746,16 @@
         <v>Otopark</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I11" t="str">
         <v/>
       </c>
       <c r="J11" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="12">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1270,13 +1270,16 @@
         <v>Park</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I27" t="str">
         <v/>
       </c>
       <c r="J27" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K27" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="28">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -915,13 +915,16 @@
         <v>Park</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I16" t="str">
         <v/>
       </c>
       <c r="J16" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="17">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1014,13 +1014,16 @@
         <v>Park</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I19" t="str">
         <v/>
       </c>
       <c r="J19" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K19" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="20">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -982,13 +982,16 @@
         <v>Park</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I18" t="str">
         <v/>
       </c>
       <c r="J18" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K18" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="19">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1419,13 +1419,16 @@
         <v>Park</v>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I31" t="str">
         <v/>
       </c>
       <c r="J31" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K31" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="32">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1148,13 +1148,16 @@
         <v>Çalılık</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I23" t="str">
         <v/>
       </c>
       <c r="J23" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K23" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="24">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1052,13 +1052,16 @@
         <v>Dere</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I20" t="str">
         <v/>
       </c>
       <c r="J20" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K20" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="21">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1221,13 +1221,16 @@
         <v>Dere</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I25" t="str">
         <v/>
       </c>
       <c r="J25" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K25" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="26">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1256,13 +1256,16 @@
         <v>Park</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I26" t="str">
         <v/>
       </c>
       <c r="J26" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K26" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="27">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1466,13 +1466,16 @@
         <v>Dere</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I32" t="str">
         <v/>
       </c>
       <c r="J32" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K32" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="33">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -1119,13 +1119,16 @@
         <v>Dere</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>Onaylandı(Firmaya İletildi)</v>
       </c>
       <c r="I22" t="str">
         <v/>
       </c>
       <c r="J22" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
+      </c>
+      <c r="K22" t="str">
+        <v>2026-04-07</v>
       </c>
     </row>
     <row r="23">

--- a/TOROSLAR.xlsx
+++ b/TOROSLAR.xlsx
@@ -466,6 +466,9 @@
       <c r="J2" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -498,6 +501,9 @@
       <c r="J3" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -530,6 +536,9 @@
       <c r="J4" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -562,6 +571,9 @@
       <c r="J5" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -594,6 +606,9 @@
       <c r="J6" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -626,6 +641,9 @@
       <c r="J7" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -658,6 +676,9 @@
       <c r="J8" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -690,6 +711,9 @@
       <c r="J9" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -722,6 +746,9 @@
       <c r="J10" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -789,6 +816,9 @@
       <c r="J12" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -821,6 +851,9 @@
       <c r="J13" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -958,6 +991,9 @@
       <c r="J17" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1095,6 +1131,9 @@
       <c r="J21" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1582,6 +1621,9 @@
       <c r="J35" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1614,6 +1656,9 @@
       <c r="J36" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
       </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1646,6 +1691,9 @@
       <c r="J37" t="str">
         <v>2.Öncelik - Plana Yakın Alan</v>
       </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1678,6 +1726,9 @@
       <c r="J38" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1710,6 +1761,9 @@
       <c r="J39" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1742,6 +1796,9 @@
       <c r="J40" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1774,6 +1831,9 @@
       <c r="J41" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1806,6 +1866,9 @@
       <c r="J42" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1838,6 +1901,9 @@
       <c r="J43" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1870,6 +1936,9 @@
       <c r="J44" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -1902,6 +1971,9 @@
       <c r="J45" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1934,6 +2006,9 @@
       <c r="J46" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1966,6 +2041,9 @@
       <c r="J47" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1998,6 +2076,9 @@
       <c r="J48" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2030,6 +2111,9 @@
       <c r="J49" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2062,6 +2146,9 @@
       <c r="J50" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2094,6 +2181,9 @@
       <c r="J51" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2126,6 +2216,9 @@
       <c r="J52" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2158,6 +2251,9 @@
       <c r="J53" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2190,6 +2286,9 @@
       <c r="J54" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2222,6 +2321,9 @@
       <c r="J55" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -2254,6 +2356,9 @@
       <c r="J56" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -2286,6 +2391,9 @@
       <c r="J57" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -2318,6 +2426,9 @@
       <c r="J58" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -2350,6 +2461,9 @@
       <c r="J59" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -2382,6 +2496,9 @@
       <c r="J60" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -2414,6 +2531,9 @@
       <c r="J61" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -2446,6 +2566,9 @@
       <c r="J62" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -2478,6 +2601,9 @@
       <c r="J63" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -2510,6 +2636,9 @@
       <c r="J64" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -2542,6 +2671,9 @@
       <c r="J65" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -2574,6 +2706,9 @@
       <c r="J66" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -2606,6 +2741,9 @@
       <c r="J67" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -2638,6 +2776,9 @@
       <c r="J68" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -2670,6 +2811,9 @@
       <c r="J69" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -2702,6 +2846,9 @@
       <c r="J70" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -2734,6 +2881,9 @@
       <c r="J71" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -2766,6 +2916,9 @@
       <c r="J72" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -2798,6 +2951,9 @@
       <c r="J73" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -2830,6 +2986,9 @@
       <c r="J74" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -2862,6 +3021,9 @@
       <c r="J75" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -2894,6 +3056,9 @@
       <c r="J76" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -2926,6 +3091,9 @@
       <c r="J77" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -2958,6 +3126,9 @@
       <c r="J78" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -2990,6 +3161,9 @@
       <c r="J79" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -3022,6 +3196,9 @@
       <c r="J80" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -3054,6 +3231,9 @@
       <c r="J81" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -3086,6 +3266,9 @@
       <c r="J82" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -3118,6 +3301,9 @@
       <c r="J83" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -3150,6 +3336,9 @@
       <c r="J84" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -3182,6 +3371,9 @@
       <c r="J85" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -3214,6 +3406,9 @@
       <c r="J86" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -3246,6 +3441,9 @@
       <c r="J87" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -3278,6 +3476,9 @@
       <c r="J88" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -3310,6 +3511,9 @@
       <c r="J89" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -3342,6 +3546,9 @@
       <c r="J90" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -3374,6 +3581,9 @@
       <c r="J91" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -3406,6 +3616,9 @@
       <c r="J92" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -3438,6 +3651,9 @@
       <c r="J93" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -3470,6 +3686,9 @@
       <c r="J94" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -3502,6 +3721,9 @@
       <c r="J95" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -3534,6 +3756,9 @@
       <c r="J96" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -3566,6 +3791,9 @@
       <c r="J97" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -3598,6 +3826,9 @@
       <c r="J98" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -3630,6 +3861,9 @@
       <c r="J99" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -3662,6 +3896,9 @@
       <c r="J100" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -3694,6 +3931,9 @@
       <c r="J101" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -3726,6 +3966,9 @@
       <c r="J102" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -3758,6 +4001,9 @@
       <c r="J103" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -3790,6 +4036,9 @@
       <c r="J104" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -3822,6 +4071,9 @@
       <c r="J105" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -3854,6 +4106,9 @@
       <c r="J106" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -3886,6 +4141,9 @@
       <c r="J107" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -3918,6 +4176,9 @@
       <c r="J108" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -3950,6 +4211,9 @@
       <c r="J109" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -3982,6 +4246,9 @@
       <c r="J110" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -4014,6 +4281,9 @@
       <c r="J111" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -4046,6 +4316,9 @@
       <c r="J112" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -4078,6 +4351,9 @@
       <c r="J113" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -4110,6 +4386,9 @@
       <c r="J114" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -4142,6 +4421,9 @@
       <c r="J115" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -4174,6 +4456,9 @@
       <c r="J116" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -4206,6 +4491,9 @@
       <c r="J117" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -4238,6 +4526,9 @@
       <c r="J118" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -4270,6 +4561,9 @@
       <c r="J119" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -4302,6 +4596,9 @@
       <c r="J120" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -4334,6 +4631,9 @@
       <c r="J121" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -4366,6 +4666,9 @@
       <c r="J122" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -4398,6 +4701,9 @@
       <c r="J123" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -4430,6 +4736,9 @@
       <c r="J124" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -4462,6 +4771,9 @@
       <c r="J125" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -4494,6 +4806,9 @@
       <c r="J126" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -4526,6 +4841,9 @@
       <c r="J127" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -4558,6 +4876,9 @@
       <c r="J128" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -4590,6 +4911,9 @@
       <c r="J129" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -4622,6 +4946,9 @@
       <c r="J130" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -4654,6 +4981,9 @@
       <c r="J131" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -4686,6 +5016,9 @@
       <c r="J132" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -4718,6 +5051,9 @@
       <c r="J133" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -4750,6 +5086,9 @@
       <c r="J134" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -4782,6 +5121,9 @@
       <c r="J135" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -4814,6 +5156,9 @@
       <c r="J136" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -4846,6 +5191,9 @@
       <c r="J137" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -4878,6 +5226,9 @@
       <c r="J138" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -4910,6 +5261,9 @@
       <c r="J139" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -4942,6 +5296,9 @@
       <c r="J140" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -4974,6 +5331,9 @@
       <c r="J141" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -5006,6 +5366,9 @@
       <c r="J142" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -5038,6 +5401,9 @@
       <c r="J143" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -5070,6 +5436,9 @@
       <c r="J144" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -5102,6 +5471,9 @@
       <c r="J145" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -5134,6 +5506,9 @@
       <c r="J146" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -5166,6 +5541,9 @@
       <c r="J147" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -5198,6 +5576,9 @@
       <c r="J148" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -5230,6 +5611,9 @@
       <c r="J149" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -5262,6 +5646,9 @@
       <c r="J150" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -5294,6 +5681,9 @@
       <c r="J151" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -5326,6 +5716,9 @@
       <c r="J152" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -5358,6 +5751,9 @@
       <c r="J153" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -5390,6 +5786,9 @@
       <c r="J154" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -5422,6 +5821,9 @@
       <c r="J155" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -5454,6 +5856,9 @@
       <c r="J156" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -5486,6 +5891,9 @@
       <c r="J157" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -5518,6 +5926,9 @@
       <c r="J158" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -5550,6 +5961,9 @@
       <c r="J159" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -5582,6 +5996,9 @@
       <c r="J160" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -5614,6 +6031,9 @@
       <c r="J161" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -5646,6 +6066,9 @@
       <c r="J162" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -5678,6 +6101,9 @@
       <c r="J163" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -5710,6 +6136,9 @@
       <c r="J164" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -5742,6 +6171,9 @@
       <c r="J165" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -5774,6 +6206,9 @@
       <c r="J166" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -5806,6 +6241,9 @@
       <c r="J167" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -5838,6 +6276,9 @@
       <c r="J168" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -5870,6 +6311,9 @@
       <c r="J169" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -5902,6 +6346,9 @@
       <c r="J170" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -5934,6 +6381,9 @@
       <c r="J171" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -5966,6 +6416,9 @@
       <c r="J172" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -5998,6 +6451,9 @@
       <c r="J173" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -6030,6 +6486,9 @@
       <c r="J174" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -6062,6 +6521,9 @@
       <c r="J175" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -6094,6 +6556,9 @@
       <c r="J176" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -6126,6 +6591,9 @@
       <c r="J177" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -6158,6 +6626,9 @@
       <c r="J178" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -6190,6 +6661,9 @@
       <c r="J179" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -6222,6 +6696,9 @@
       <c r="J180" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -6254,6 +6731,9 @@
       <c r="J181" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -6286,6 +6766,9 @@
       <c r="J182" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -6318,6 +6801,9 @@
       <c r="J183" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -6350,6 +6836,9 @@
       <c r="J184" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -6382,6 +6871,9 @@
       <c r="J185" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -6414,6 +6906,9 @@
       <c r="J186" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -6446,6 +6941,9 @@
       <c r="J187" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -6478,6 +6976,9 @@
       <c r="J188" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -6510,6 +7011,9 @@
       <c r="J189" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -6542,6 +7046,9 @@
       <c r="J190" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -6574,6 +7081,9 @@
       <c r="J191" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -6606,6 +7116,9 @@
       <c r="J192" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -6638,6 +7151,9 @@
       <c r="J193" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -6670,6 +7186,9 @@
       <c r="J194" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -6702,6 +7221,9 @@
       <c r="J195" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -6734,6 +7256,9 @@
       <c r="J196" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -6766,6 +7291,9 @@
       <c r="J197" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -6798,6 +7326,9 @@
       <c r="J198" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -6830,6 +7361,9 @@
       <c r="J199" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -6862,6 +7396,9 @@
       <c r="J200" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -6894,6 +7431,9 @@
       <c r="J201" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -6926,6 +7466,9 @@
       <c r="J202" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -6958,6 +7501,9 @@
       <c r="J203" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -6990,6 +7536,9 @@
       <c r="J204" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -7022,6 +7571,9 @@
       <c r="J205" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -7054,6 +7606,9 @@
       <c r="J206" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -7086,6 +7641,9 @@
       <c r="J207" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -7118,6 +7676,9 @@
       <c r="J208" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -7150,6 +7711,9 @@
       <c r="J209" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -7182,6 +7746,9 @@
       <c r="J210" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -7214,6 +7781,9 @@
       <c r="J211" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -7246,6 +7816,9 @@
       <c r="J212" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -7278,6 +7851,9 @@
       <c r="J213" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -7310,6 +7886,9 @@
       <c r="J214" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -7342,6 +7921,9 @@
       <c r="J215" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -7374,6 +7956,9 @@
       <c r="J216" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -7406,6 +7991,9 @@
       <c r="J217" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -7438,6 +8026,9 @@
       <c r="J218" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -7470,6 +8061,9 @@
       <c r="J219" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -7502,6 +8096,9 @@
       <c r="J220" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -7534,6 +8131,9 @@
       <c r="J221" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -7566,6 +8166,9 @@
       <c r="J222" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -7598,6 +8201,9 @@
       <c r="J223" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -7630,6 +8236,9 @@
       <c r="J224" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -7662,6 +8271,9 @@
       <c r="J225" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -7694,6 +8306,9 @@
       <c r="J226" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -7726,6 +8341,9 @@
       <c r="J227" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -7758,6 +8376,9 @@
       <c r="J228" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -7790,6 +8411,9 @@
       <c r="J229" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -7822,6 +8446,9 @@
       <c r="J230" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -7854,6 +8481,9 @@
       <c r="J231" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -7886,6 +8516,9 @@
       <c r="J232" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -7918,6 +8551,9 @@
       <c r="J233" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K233" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -7950,6 +8586,9 @@
       <c r="J234" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K234" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -7982,6 +8621,9 @@
       <c r="J235" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K235" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -8014,6 +8656,9 @@
       <c r="J236" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K236" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -8046,6 +8691,9 @@
       <c r="J237" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K237" t="str">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -8078,6 +8726,9 @@
       <c r="J238" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K238" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -8110,6 +8761,9 @@
       <c r="J239" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K239" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -8142,6 +8796,9 @@
       <c r="J240" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K240" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -8174,6 +8831,9 @@
       <c r="J241" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K241" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -8206,6 +8866,9 @@
       <c r="J242" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K242" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -8238,6 +8901,9 @@
       <c r="J243" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K243" t="str">
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -8270,6 +8936,9 @@
       <c r="J244" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K244" t="str">
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -8302,6 +8971,9 @@
       <c r="J245" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K245" t="str">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -8334,6 +9006,9 @@
       <c r="J246" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K246" t="str">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -8366,6 +9041,9 @@
       <c r="J247" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K247" t="str">
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -8398,6 +9076,9 @@
       <c r="J248" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K248" t="str">
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -8430,6 +9111,9 @@
       <c r="J249" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K249" t="str">
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -8462,6 +9146,9 @@
       <c r="J250" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K250" t="str">
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -8494,6 +9181,9 @@
       <c r="J251" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K251" t="str">
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -8526,6 +9216,9 @@
       <c r="J252" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K252" t="str">
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -8558,6 +9251,9 @@
       <c r="J253" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K253" t="str">
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -8590,6 +9286,9 @@
       <c r="J254" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K254" t="str">
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -8622,6 +9321,9 @@
       <c r="J255" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K255" t="str">
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -8654,6 +9356,9 @@
       <c r="J256" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K256" t="str">
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -8686,6 +9391,9 @@
       <c r="J257" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K257" t="str">
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -8718,6 +9426,9 @@
       <c r="J258" t="str">
         <v>3.Öncelik - Plansız Değerlendirilebilir Alan</v>
       </c>
+      <c r="K258" t="str">
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -8748,6 +9459,9 @@
         <v/>
       </c>
       <c r="J259" t="str">
+        <v/>
+      </c>
+      <c r="K259" t="str">
         <v/>
       </c>
     </row>
